--- a/sheets/조재수대금교본/검수/회룡포.xlsx
+++ b/sheets/조재수대금교본/검수/회룡포.xlsx
@@ -3857,7 +3857,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -3916,11 +3916,7 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -3928,17 +3924,9 @@
         </is>
       </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
@@ -3969,16 +3957,11 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C5" s="24"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
@@ -3988,15 +3971,13 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -4012,16 +3993,11 @@
       <c r="Q5" s="24"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="S5" s="24"/>
-      <c r="T5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
     <row r="6" ht="106.4" customHeight="true">
@@ -4055,15 +4031,11 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -4071,11 +4043,7 @@
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
@@ -4083,11 +4051,7 @@
         </is>
       </c>
       <c r="S6" s="22"/>
-      <c r="T6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T6" s="21"/>
       <c r="U6" s="22"/>
     </row>
     <row r="7" ht="106.4" customHeight="true">
@@ -4145,8 +4109,7 @@
       <c r="S7" s="23"/>
       <c r="T7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-Z</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U7" s="23"/>
@@ -4159,11 +4122,7 @@
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -4174,8 +4133,7 @@
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -4188,8 +4146,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -4202,8 +4159,7 @@
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
@@ -4286,11 +4242,7 @@
     </row>
     <row r="10" ht="106.4" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
@@ -4368,8 +4320,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-ﾉ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4401,11 +4352,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="22"/>
       <c r="F12" s="21"/>
       <c r="G12" s="22"/>
@@ -4475,31 +4422,15 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
@@ -4511,11 +4442,7 @@
       <c r="Q14" s="24"/>
       <c r="R14" s="21"/>
       <c r="S14" s="24"/>
-      <c r="T14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/회룡포.xlsx
+++ b/sheets/조재수대금교본/검수/회룡포.xlsx
@@ -3857,7 +3857,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -3916,7 +3916,11 @@
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -3924,9 +3928,17 @@
         </is>
       </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
@@ -3997,7 +4009,11 @@
         </is>
       </c>
       <c r="S5" s="24"/>
-      <c r="T5" s="21"/>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U5" s="24"/>
     </row>
     <row r="6" ht="106.4" customHeight="true">
@@ -4031,11 +4047,15 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -4043,7 +4063,11 @@
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
@@ -4051,7 +4075,11 @@
         </is>
       </c>
       <c r="S6" s="22"/>
-      <c r="T6" s="21"/>
+      <c r="T6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U6" s="22"/>
     </row>
     <row r="7" ht="106.4" customHeight="true">
@@ -4109,7 +4137,8 @@
       <c r="S7" s="23"/>
       <c r="T7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+Z</t>
         </is>
       </c>
       <c r="U7" s="23"/>
@@ -4320,7 +4349,8 @@
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+ﾉ</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4352,7 +4382,11 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="21"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21"/>
       <c r="G12" s="22"/>

--- a/sheets/조재수대금교본/검수/회룡포.xlsx
+++ b/sheets/조재수대금교본/검수/회룡포.xlsx
@@ -3789,32 +3789,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4448,7 +4448,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4485,6 +4485,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
 </worksheet>
 </file>